--- a/Data/EXCEL/Transfer/salemon/20240711/4583-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/4583-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61868208-7AB8-4EB3-B063-09F4AF9FE302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E913E4A-6B67-4CB4-9695-1A220068E86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{0788A8DB-557C-4E56-A9C8-D0C7E84097E3}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{D35702FB-33C3-49A1-9A2B-11AEFF6044FF}"/>
   </bookViews>
   <sheets>
     <sheet name="4583-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,22 +1261,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8405A46-E039-43D1-96ED-1873251F7162}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB8CF32-02ED-4013-8648-EE4CDCED9A85}">
   <dimension ref="A1:Q99"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1303,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1424,7 +1424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>-21.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>-19.2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>-19.2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>-21.8</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>-22.4</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>-22.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>-20.8</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>-23.8</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>-24.6</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>-37.799999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>-3.03</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>-4.63</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>-6.9</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3862,247 +3862,247 @@
         <v>-7.19</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <v>44075</v>
       </c>
